--- a/web/会员权益.xlsx
+++ b/web/会员权益.xlsx
@@ -38,7 +38,7 @@
     <t>金芒果</t>
   </si>
   <si>
-    <t>黑金芒果</t>
+    <t>黑芒果</t>
   </si>
   <si>
     <t>手搓旅游攻略</t>

--- a/web/会员权益.xlsx
+++ b/web/会员权益.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
-  <si>
-    <t>芒果派</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
+  <si>
+    <t>权益项目</t>
+  </si>
+  <si>
+    <t>芒果 π</t>
   </si>
   <si>
     <t>青芒果</t>
@@ -41,34 +44,127 @@
     <t>黑芒果</t>
   </si>
   <si>
-    <t>手搓旅游攻略</t>
-  </si>
-  <si>
-    <t>√</t>
-  </si>
-  <si>
-    <t>酒店预定</t>
-  </si>
-  <si>
-    <t>首单8.8折</t>
-  </si>
-  <si>
-    <t>全场优惠</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>接送机</t>
-  </si>
-  <si>
-    <t>半价</t>
+    <t>专属会员标签</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>会员价展示</t>
+  </si>
+  <si>
+    <t>基础积分累积</t>
+  </si>
+  <si>
+    <t>积分商城基础区</t>
+  </si>
+  <si>
+    <t>专属客服通道</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>生日礼券</t>
+  </si>
+  <si>
+    <t>积分商城进阶区</t>
+  </si>
+  <si>
+    <t>免费接送机(次/年)</t>
+  </si>
+  <si>
+    <t>租车折扣</t>
+  </si>
+  <si>
+    <t>95折</t>
+  </si>
+  <si>
+    <t>92折</t>
+  </si>
+  <si>
+    <t>88折</t>
+  </si>
+  <si>
+    <t>85折</t>
+  </si>
+  <si>
+    <t>优先预订权</t>
+  </si>
+  <si>
+    <t>升舱体验券</t>
+  </si>
+  <si>
+    <t>异地还车手续费减免</t>
+  </si>
+  <si>
+    <t>8.8 折</t>
+  </si>
+  <si>
+    <t>8.5 折</t>
+  </si>
+  <si>
+    <t>8 折</t>
+  </si>
+  <si>
+    <t>免费取送车</t>
+  </si>
+  <si>
+    <t>7 天以上订单</t>
+  </si>
+  <si>
+    <t>3 天以上订单</t>
+  </si>
+  <si>
+    <t>所有订单</t>
+  </si>
+  <si>
+    <t>违章代办服务费</t>
+  </si>
+  <si>
+    <t>标准收费</t>
+  </si>
+  <si>
+    <t>5 折</t>
+  </si>
+  <si>
+    <t>3 折</t>
   </si>
   <si>
     <t>免费</t>
   </si>
   <si>
-    <t>专属秘书</t>
+    <t>事故停运费减免</t>
+  </si>
+  <si>
+    <t>减免 10%</t>
+  </si>
+  <si>
+    <t>减免 20%</t>
+  </si>
+  <si>
+    <t>减免 30%</t>
+  </si>
+  <si>
+    <t>免押金额度</t>
+  </si>
+  <si>
+    <t>5千</t>
+  </si>
+  <si>
+    <t>1万</t>
+  </si>
+  <si>
+    <t>2万</t>
+  </si>
+  <si>
+    <t>专属活动邀约</t>
+  </si>
+  <si>
+    <t>试驾/品鉴</t>
+  </si>
+  <si>
+    <t>晚宴/赛道日</t>
   </si>
 </sst>
 </file>
@@ -81,13 +177,34 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFD4AF37"/>
+      <name val="Noto Sans SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Noto Sans SC"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -234,12 +351,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4AF37"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8860B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2D2D2D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -554,61 +689,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -617,76 +743,97 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1213,126 +1360,316 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="19.8076923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="B1" t="s">
+    <row r="1" ht="18" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" ht="31" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="31" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" ht="31" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/web/会员权益.xlsx
+++ b/web/会员权益.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
   <si>
     <t>权益项目</t>
   </si>
@@ -51,12 +51,6 @@
   </si>
   <si>
     <t>会员价展示</t>
-  </si>
-  <si>
-    <t>基础积分累积</t>
-  </si>
-  <si>
-    <t>积分商城基础区</t>
   </si>
   <si>
     <t>专属客服通道</t>
@@ -177,7 +171,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +198,13 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Noto Sans SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -689,137 +690,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,6 +834,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1360,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="19.8076923076923" customWidth="1"/>
@@ -1422,7 +1426,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>6</v>
@@ -1436,10 +1440,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -1453,10 +1457,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>6</v>
@@ -1464,7 +1468,7 @@
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1473,16 +1477,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1490,50 +1494,50 @@
         <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1541,135 +1545,101 @@
         <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" ht="31" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="31" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="31" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" ht="31" spans="1:5">
-      <c r="A18" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
